--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46081.69430476496</v>
+        <v>46081.73190847513</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46081.69430476496</v>
+        <v>46081.73190847513</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46081.69430476496</v>
+        <v>46081.73190847513</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46081.69430476496</v>
+        <v>46081.73190847513</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46081.69430476496</v>
+        <v>46081.73190847513</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46081.69430476496</v>
+        <v>46081.73190847513</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46081.69430476496</v>
+        <v>46081.73190847513</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46081.73190847513</v>
+        <v>46081.78379952876</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46081.73190847513</v>
+        <v>46081.78379952876</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46081.73190847513</v>
+        <v>46081.78379952876</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46081.73190847513</v>
+        <v>46081.78379952876</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46081.73190847513</v>
+        <v>46081.78379952876</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46081.73190847513</v>
+        <v>46081.78379952876</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46081.73190847513</v>
+        <v>46081.78379952876</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46081.78379952876</v>
+        <v>46081.81281211404</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46081.78379952876</v>
+        <v>46081.81281211404</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46081.78379952876</v>
+        <v>46081.81281211404</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46081.78379952876</v>
+        <v>46081.81281211404</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46081.78379952876</v>
+        <v>46081.81281211404</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46081.78379952876</v>
+        <v>46081.81281211404</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46081.78379952876</v>
+        <v>46081.81281211404</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46081.81281211404</v>
+        <v>46081.85934833413</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46081.81281211404</v>
+        <v>46081.85934833413</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46081.81281211404</v>
+        <v>46081.85934833413</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46081.81281211404</v>
+        <v>46081.85934833413</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46081.81281211404</v>
+        <v>46081.85934833413</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46081.81281211404</v>
+        <v>46081.85934833413</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46081.81281211404</v>
+        <v>46081.85934833413</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46081.85934833413</v>
+        <v>46081.89812166412</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46081.85934833413</v>
+        <v>46081.89812166412</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46081.85934833413</v>
+        <v>46081.89812166412</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46081.85934833413</v>
+        <v>46081.89812166412</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46081.85934833413</v>
+        <v>46081.89812166412</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46081.85934833413</v>
+        <v>46081.89812166412</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46081.85934833413</v>
+        <v>46081.89812166412</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46081.89812166412</v>
+        <v>46083.32910358971</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46081.89812166412</v>
+        <v>46083.32910358971</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46081.89812166412</v>
+        <v>46083.32910358971</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46081.89812166412</v>
+        <v>46083.32910358971</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46081.89812166412</v>
+        <v>46083.32910358971</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46081.89812166412</v>
+        <v>46083.32910358971</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46081.89812166412</v>
+        <v>46083.32910358971</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.32910358971</v>
+        <v>46083.37508773597</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.32910358971</v>
+        <v>46083.37508773597</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.32910358971</v>
+        <v>46083.37508773597</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.32910358971</v>
+        <v>46083.37508773597</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.32910358971</v>
+        <v>46083.37508773597</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.32910358971</v>
+        <v>46083.37508773597</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.32910358971</v>
+        <v>46083.37508773597</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.37508773597</v>
+        <v>46083.41974353771</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.37508773597</v>
+        <v>46083.41974353771</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.37508773597</v>
+        <v>46083.41974353771</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.37508773597</v>
+        <v>46083.41974353771</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.37508773597</v>
+        <v>46083.41974353771</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.37508773597</v>
+        <v>46083.41974353771</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.37508773597</v>
+        <v>46083.41974353771</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.41974353771</v>
+        <v>46083.45868348486</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.41974353771</v>
+        <v>46083.45868348486</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.41974353771</v>
+        <v>46083.45868348486</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.41974353771</v>
+        <v>46083.45868348486</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.41974353771</v>
+        <v>46083.45868348486</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.41974353771</v>
+        <v>46083.45868348486</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.41974353771</v>
+        <v>46083.45868348486</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.45868348486</v>
+        <v>46083.48694277374</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.45868348486</v>
+        <v>46083.48694277374</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.45868348486</v>
+        <v>46083.48694277374</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.45868348486</v>
+        <v>46083.48694277374</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.45868348486</v>
+        <v>46083.48694277374</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.45868348486</v>
+        <v>46083.48694277374</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.45868348486</v>
+        <v>46083.48694277374</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.48694277374</v>
+        <v>46083.55761445255</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.48694277374</v>
+        <v>46083.55761445255</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,7 +637,7 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.48694277374</v>
+        <v>46083.55761445255</v>
       </c>
       <c r="G5" t="n">
         <v>2.89</v>
@@ -677,7 +677,7 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.48694277374</v>
+        <v>46083.55761445255</v>
       </c>
       <c r="G6" t="n">
         <v>58.84</v>
@@ -717,7 +717,7 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.48694277374</v>
+        <v>46083.55761445255</v>
       </c>
       <c r="G7" t="n">
         <v>11.82</v>
@@ -757,7 +757,7 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.48694277374</v>
+        <v>46083.55761445255</v>
       </c>
       <c r="G8" t="n">
         <v>22.75</v>
@@ -797,7 +797,7 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.48694277374</v>
+        <v>46083.55761445255</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.55761445255</v>
+        <v>46083.62341295267</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,20 +597,20 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.55761445255</v>
+        <v>46083.62341295267</v>
       </c>
       <c r="G4" t="n">
-        <v>7.08</v>
+        <v>6.9968</v>
       </c>
       <c r="H4" t="n">
-        <v>2039.04</v>
+        <v>2015.0784</v>
       </c>
       <c r="I4" t="n">
         <v>6.66</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.06626506024096401</v>
+        <v>0.05373493975903632</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
@@ -637,20 +637,20 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.55761445255</v>
+        <v>46083.62341295267</v>
       </c>
       <c r="G5" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>1346.74</v>
+        <v>1323.44</v>
       </c>
       <c r="I5" t="n">
         <v>2.77128</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.05822043207616256</v>
+        <v>0.03991212010252654</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
@@ -677,20 +677,20 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.55761445255</v>
+        <v>46083.62341295267</v>
       </c>
       <c r="G6" t="n">
-        <v>58.84</v>
+        <v>57.83</v>
       </c>
       <c r="H6" t="n">
-        <v>2294.76</v>
+        <v>2255.37</v>
       </c>
       <c r="I6" t="n">
         <v>53.19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.1564465408805031</v>
+        <v>0.1365959119496853</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
@@ -717,20 +717,20 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.55761445255</v>
+        <v>46083.62341295267</v>
       </c>
       <c r="G7" t="n">
-        <v>11.82</v>
+        <v>11.855</v>
       </c>
       <c r="H7" t="n">
-        <v>2009.4</v>
+        <v>2015.35</v>
       </c>
       <c r="I7" t="n">
         <v>10.746</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.005957446808510625</v>
+        <v>0.008936170212765937</v>
       </c>
       <c r="L7" t="n">
         <v>9.667</v>
@@ -757,20 +757,20 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.55761445255</v>
+        <v>46083.62341295267</v>
       </c>
       <c r="G8" t="n">
-        <v>22.75</v>
+        <v>22.55</v>
       </c>
       <c r="H8" t="n">
-        <v>2024.75</v>
+        <v>2006.95</v>
       </c>
       <c r="I8" t="n">
         <v>20.52</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.1684643040575244</v>
+        <v>0.1581920903954803</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -797,20 +797,20 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.55761445255</v>
+        <v>46083.62341295267</v>
       </c>
       <c r="G9" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="H9" t="n">
-        <v>1778.4</v>
+        <v>1856.4</v>
       </c>
       <c r="I9" t="n">
         <v>5.364</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.01324326726513214</v>
+        <v>0.05768376144342735</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.62341295267</v>
+        <v>46083.66283780524</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,20 +597,20 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.62341295267</v>
+        <v>46083.66283780524</v>
       </c>
       <c r="G4" t="n">
-        <v>6.9968</v>
+        <v>6.985</v>
       </c>
       <c r="H4" t="n">
-        <v>2015.0784</v>
+        <v>2011.68</v>
       </c>
       <c r="I4" t="n">
         <v>6.66</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.05373493975903632</v>
+        <v>0.0519578313253013</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
@@ -637,20 +637,20 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.62341295267</v>
+        <v>46083.66283780524</v>
       </c>
       <c r="G5" t="n">
-        <v>2.84</v>
+        <v>2.895</v>
       </c>
       <c r="H5" t="n">
-        <v>1323.44</v>
+        <v>1349.07</v>
       </c>
       <c r="I5" t="n">
         <v>2.77128</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.03991212010252654</v>
+        <v>0.06005126327352617</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
@@ -677,20 +677,20 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.62341295267</v>
+        <v>46083.66283780524</v>
       </c>
       <c r="G6" t="n">
-        <v>57.83</v>
+        <v>56.665</v>
       </c>
       <c r="H6" t="n">
-        <v>2255.37</v>
+        <v>2209.935</v>
       </c>
       <c r="I6" t="n">
         <v>53.19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.1365959119496853</v>
+        <v>0.113698899371069</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
@@ -717,20 +717,20 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.62341295267</v>
+        <v>46083.66283780524</v>
       </c>
       <c r="G7" t="n">
-        <v>11.855</v>
+        <v>12.33</v>
       </c>
       <c r="H7" t="n">
-        <v>2015.35</v>
+        <v>2096.1</v>
       </c>
       <c r="I7" t="n">
-        <v>10.746</v>
+        <v>11.097</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.008936170212765937</v>
+        <v>0.04936170212765956</v>
       </c>
       <c r="L7" t="n">
         <v>9.667</v>
@@ -757,20 +757,20 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.62341295267</v>
+        <v>46083.66283780524</v>
       </c>
       <c r="G8" t="n">
-        <v>22.55</v>
+        <v>22.315</v>
       </c>
       <c r="H8" t="n">
-        <v>2006.95</v>
+        <v>1986.035</v>
       </c>
       <c r="I8" t="n">
         <v>20.52</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.1581920903954803</v>
+        <v>0.1461222393425785</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -797,20 +797,20 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.62341295267</v>
+        <v>46083.66283780524</v>
       </c>
       <c r="G9" t="n">
-        <v>5.95</v>
+        <v>6.18</v>
       </c>
       <c r="H9" t="n">
-        <v>1856.4</v>
+        <v>1928.16</v>
       </c>
       <c r="I9" t="n">
-        <v>5.364</v>
+        <v>5.562</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.05768376144342735</v>
+        <v>0.09856901608745883</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.66283780524</v>
+        <v>46083.71076576615</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,20 +597,20 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.66283780524</v>
+        <v>46083.71076576615</v>
       </c>
       <c r="G4" t="n">
-        <v>6.985</v>
+        <v>7.03</v>
       </c>
       <c r="H4" t="n">
-        <v>2011.68</v>
+        <v>2024.64</v>
       </c>
       <c r="I4" t="n">
         <v>6.66</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.0519578313253013</v>
+        <v>0.05873493975903621</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
@@ -637,20 +637,20 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.66283780524</v>
+        <v>46083.71076576615</v>
       </c>
       <c r="G5" t="n">
-        <v>2.895</v>
+        <v>2.955</v>
       </c>
       <c r="H5" t="n">
-        <v>1349.07</v>
+        <v>1377.03</v>
       </c>
       <c r="I5" t="n">
         <v>2.77128</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.06005126327352617</v>
+        <v>0.0820212376418894</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
@@ -677,20 +677,20 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.66283780524</v>
+        <v>46083.71076576615</v>
       </c>
       <c r="G6" t="n">
-        <v>56.665</v>
+        <v>56.86</v>
       </c>
       <c r="H6" t="n">
-        <v>2209.935</v>
+        <v>2217.54</v>
       </c>
       <c r="I6" t="n">
         <v>53.19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.113698899371069</v>
+        <v>0.1175314465408805</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
@@ -717,20 +717,20 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.66283780524</v>
+        <v>46083.71076576615</v>
       </c>
       <c r="G7" t="n">
-        <v>12.33</v>
+        <v>12.29</v>
       </c>
       <c r="H7" t="n">
-        <v>2096.1</v>
+        <v>2089.3</v>
       </c>
       <c r="I7" t="n">
         <v>11.097</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.04936170212765956</v>
+        <v>0.04595744680851066</v>
       </c>
       <c r="L7" t="n">
         <v>9.667</v>
@@ -757,20 +757,20 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.66283780524</v>
+        <v>46083.71076576615</v>
       </c>
       <c r="G8" t="n">
-        <v>22.315</v>
+        <v>22.232</v>
       </c>
       <c r="H8" t="n">
-        <v>1986.035</v>
+        <v>1978.648</v>
       </c>
       <c r="I8" t="n">
         <v>20.52</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.1461222393425785</v>
+        <v>0.1418592706728301</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -797,20 +797,20 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.66283780524</v>
+        <v>46083.71076576615</v>
       </c>
       <c r="G9" t="n">
-        <v>6.18</v>
+        <v>6.19</v>
       </c>
       <c r="H9" t="n">
-        <v>1928.16</v>
+        <v>1931.28</v>
       </c>
       <c r="I9" t="n">
-        <v>5.562</v>
+        <v>5.571000000000001</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.09856901608745883</v>
+        <v>0.1003466358545908</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.71076576615</v>
+        <v>46083.74867088813</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,20 +597,20 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.71076576615</v>
+        <v>46083.74867088813</v>
       </c>
       <c r="G4" t="n">
-        <v>7.03</v>
+        <v>7.07</v>
       </c>
       <c r="H4" t="n">
-        <v>2024.64</v>
+        <v>2036.16</v>
       </c>
       <c r="I4" t="n">
         <v>6.66</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.05873493975903621</v>
+        <v>0.06475903614457845</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
@@ -637,20 +637,20 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.71076576615</v>
+        <v>46083.74867088813</v>
       </c>
       <c r="G5" t="n">
-        <v>2.955</v>
+        <v>2.945</v>
       </c>
       <c r="H5" t="n">
-        <v>1377.03</v>
+        <v>1372.37</v>
       </c>
       <c r="I5" t="n">
         <v>2.77128</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.0820212376418894</v>
+        <v>0.07835957524716219</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
@@ -677,20 +677,20 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.71076576615</v>
+        <v>46083.74867088813</v>
       </c>
       <c r="G6" t="n">
-        <v>56.86</v>
+        <v>56.755</v>
       </c>
       <c r="H6" t="n">
-        <v>2217.54</v>
+        <v>2213.445</v>
       </c>
       <c r="I6" t="n">
         <v>53.19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.1175314465408805</v>
+        <v>0.1154677672955975</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
@@ -717,20 +717,20 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.71076576615</v>
+        <v>46083.74867088813</v>
       </c>
       <c r="G7" t="n">
-        <v>12.29</v>
+        <v>12.37</v>
       </c>
       <c r="H7" t="n">
-        <v>2089.3</v>
+        <v>2102.9</v>
       </c>
       <c r="I7" t="n">
-        <v>11.097</v>
+        <v>11.133</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.04595744680851066</v>
+        <v>0.05276595744680845</v>
       </c>
       <c r="L7" t="n">
         <v>9.667</v>
@@ -757,20 +757,20 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.71076576615</v>
+        <v>46083.74867088813</v>
       </c>
       <c r="G8" t="n">
-        <v>22.232</v>
+        <v>22.12</v>
       </c>
       <c r="H8" t="n">
-        <v>1978.648</v>
+        <v>1968.68</v>
       </c>
       <c r="I8" t="n">
         <v>20.52</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.1418592706728301</v>
+        <v>0.1361068310220854</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -797,20 +797,20 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.71076576615</v>
+        <v>46083.74867088813</v>
       </c>
       <c r="G9" t="n">
-        <v>6.19</v>
+        <v>6.22</v>
       </c>
       <c r="H9" t="n">
-        <v>1931.28</v>
+        <v>1940.64</v>
       </c>
       <c r="I9" t="n">
-        <v>5.571000000000001</v>
+        <v>5.598</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.1003466358545908</v>
+        <v>0.1056794951559861</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.74867088813</v>
+        <v>46083.79485592779</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,20 +597,20 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.74867088813</v>
+        <v>46083.79485592779</v>
       </c>
       <c r="G4" t="n">
-        <v>7.07</v>
+        <v>7.09</v>
       </c>
       <c r="H4" t="n">
-        <v>2036.16</v>
+        <v>2041.92</v>
       </c>
       <c r="I4" t="n">
         <v>6.66</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.06475903614457845</v>
+        <v>0.06777108433734935</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
@@ -637,20 +637,20 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.74867088813</v>
+        <v>46083.79485592779</v>
       </c>
       <c r="G5" t="n">
-        <v>2.945</v>
+        <v>2.935</v>
       </c>
       <c r="H5" t="n">
-        <v>1372.37</v>
+        <v>1367.71</v>
       </c>
       <c r="I5" t="n">
         <v>2.77128</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.07835957524716219</v>
+        <v>0.07469791285243499</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
@@ -677,20 +677,20 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.74867088813</v>
+        <v>46083.79485592779</v>
       </c>
       <c r="G6" t="n">
-        <v>56.755</v>
+        <v>57.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2213.445</v>
+        <v>2224.95</v>
       </c>
       <c r="I6" t="n">
         <v>53.19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.1154677672955975</v>
+        <v>0.1212657232704402</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
@@ -717,20 +717,20 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.74867088813</v>
+        <v>46083.79485592779</v>
       </c>
       <c r="G7" t="n">
-        <v>12.37</v>
+        <v>12.4399</v>
       </c>
       <c r="H7" t="n">
-        <v>2102.9</v>
+        <v>2114.783</v>
       </c>
       <c r="I7" t="n">
-        <v>11.133</v>
+        <v>11.19591</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.05276595744680845</v>
+        <v>0.0587148936170212</v>
       </c>
       <c r="L7" t="n">
         <v>9.667</v>
@@ -757,20 +757,20 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.74867088813</v>
+        <v>46083.79485592779</v>
       </c>
       <c r="G8" t="n">
-        <v>22.12</v>
+        <v>22.26</v>
       </c>
       <c r="H8" t="n">
-        <v>1968.68</v>
+        <v>1981.14</v>
       </c>
       <c r="I8" t="n">
         <v>20.52</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.1361068310220854</v>
+        <v>0.1432973805855162</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -797,20 +797,20 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.74867088813</v>
+        <v>46083.79485592779</v>
       </c>
       <c r="G9" t="n">
-        <v>6.22</v>
+        <v>6.28</v>
       </c>
       <c r="H9" t="n">
-        <v>1940.64</v>
+        <v>1959.36</v>
       </c>
       <c r="I9" t="n">
-        <v>5.598</v>
+        <v>5.652</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.1056794951559861</v>
+        <v>0.116345213758777</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.79485592779</v>
+        <v>46083.82500935384</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,20 +597,20 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.79485592779</v>
+        <v>46083.82500935384</v>
       </c>
       <c r="G4" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="H4" t="n">
-        <v>2041.92</v>
+        <v>2039.04</v>
       </c>
       <c r="I4" t="n">
         <v>6.66</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.06777108433734935</v>
+        <v>0.06626506024096401</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
@@ -637,20 +637,20 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.79485592779</v>
+        <v>46083.82500935384</v>
       </c>
       <c r="G5" t="n">
-        <v>2.935</v>
+        <v>2.955</v>
       </c>
       <c r="H5" t="n">
-        <v>1367.71</v>
+        <v>1377.03</v>
       </c>
       <c r="I5" t="n">
         <v>2.77128</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.07469791285243499</v>
+        <v>0.0820212376418894</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
@@ -677,20 +677,20 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.79485592779</v>
+        <v>46083.82500935384</v>
       </c>
       <c r="G6" t="n">
-        <v>57.05</v>
+        <v>57.63</v>
       </c>
       <c r="H6" t="n">
-        <v>2224.95</v>
+        <v>2247.57</v>
       </c>
       <c r="I6" t="n">
         <v>53.19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.1212657232704402</v>
+        <v>0.1326650943396226</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
@@ -717,20 +717,20 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.79485592779</v>
+        <v>46083.82500935384</v>
       </c>
       <c r="G7" t="n">
-        <v>12.4399</v>
+        <v>12.36</v>
       </c>
       <c r="H7" t="n">
-        <v>2114.783</v>
+        <v>2101.2</v>
       </c>
       <c r="I7" t="n">
         <v>11.19591</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.0587148936170212</v>
+        <v>0.05191489361702128</v>
       </c>
       <c r="L7" t="n">
         <v>9.667</v>
@@ -757,20 +757,20 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.79485592779</v>
+        <v>46083.82500935384</v>
       </c>
       <c r="G8" t="n">
-        <v>22.26</v>
+        <v>22.4807</v>
       </c>
       <c r="H8" t="n">
-        <v>1981.14</v>
+        <v>2000.7823</v>
       </c>
       <c r="I8" t="n">
         <v>20.52</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.1432973805855162</v>
+        <v>0.154632768361582</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -797,20 +797,20 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.79485592779</v>
+        <v>46083.82500935384</v>
       </c>
       <c r="G9" t="n">
-        <v>6.28</v>
+        <v>6.42</v>
       </c>
       <c r="H9" t="n">
-        <v>1959.36</v>
+        <v>2003.04</v>
       </c>
       <c r="I9" t="n">
-        <v>5.652</v>
+        <v>5.778</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.116345213758777</v>
+        <v>0.1412318904986223</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.82500935384</v>
+        <v>46083.86850438212</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,7 +597,7 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.82500935384</v>
+        <v>46083.86850438212</v>
       </c>
       <c r="G4" t="n">
         <v>7.08</v>
@@ -637,20 +637,20 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.82500935384</v>
+        <v>46083.86850438212</v>
       </c>
       <c r="G5" t="n">
-        <v>2.955</v>
+        <v>2.96</v>
       </c>
       <c r="H5" t="n">
-        <v>1377.03</v>
+        <v>1379.36</v>
       </c>
       <c r="I5" t="n">
         <v>2.77128</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.0820212376418894</v>
+        <v>0.083852068839253</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
@@ -677,20 +677,20 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.82500935384</v>
+        <v>46083.86850438212</v>
       </c>
       <c r="G6" t="n">
-        <v>57.63</v>
+        <v>57.78</v>
       </c>
       <c r="H6" t="n">
-        <v>2247.57</v>
+        <v>2253.42</v>
       </c>
       <c r="I6" t="n">
         <v>53.19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.1326650943396226</v>
+        <v>0.1356132075471699</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
@@ -717,20 +717,20 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.82500935384</v>
+        <v>46083.86850438212</v>
       </c>
       <c r="G7" t="n">
-        <v>12.36</v>
+        <v>12.68</v>
       </c>
       <c r="H7" t="n">
-        <v>2101.2</v>
+        <v>2155.6</v>
       </c>
       <c r="I7" t="n">
-        <v>11.19591</v>
+        <v>11.412</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.05191489361702128</v>
+        <v>0.07914893617021268</v>
       </c>
       <c r="L7" t="n">
         <v>9.667</v>
@@ -757,20 +757,20 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.82500935384</v>
+        <v>46083.86850438212</v>
       </c>
       <c r="G8" t="n">
-        <v>22.4807</v>
+        <v>22.48</v>
       </c>
       <c r="H8" t="n">
-        <v>2000.7823</v>
+        <v>2000.72</v>
       </c>
       <c r="I8" t="n">
         <v>20.52</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.154632768361582</v>
+        <v>0.1545968156137649</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -797,20 +797,20 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.82500935384</v>
+        <v>46083.86850438212</v>
       </c>
       <c r="G9" t="n">
-        <v>6.42</v>
+        <v>6.44</v>
       </c>
       <c r="H9" t="n">
-        <v>2003.04</v>
+        <v>2009.28</v>
       </c>
       <c r="I9" t="n">
-        <v>5.778</v>
+        <v>5.796</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.1412318904986223</v>
+        <v>0.144787130032886</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>

--- a/data/depot.xlsx
+++ b/data/depot.xlsx
@@ -517,7 +517,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46083.86850438212</v>
+        <v>46083.90854394721</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -597,20 +597,20 @@
         <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46083.86850438212</v>
+        <v>46083.90854394721</v>
       </c>
       <c r="G4" t="n">
-        <v>7.08</v>
+        <v>7.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2039.04</v>
+        <v>2044.8</v>
       </c>
       <c r="I4" t="n">
         <v>6.66</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.06626506024096401</v>
+        <v>0.06927710843373491</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
@@ -637,20 +637,20 @@
         <v>466</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46083.86850438212</v>
+        <v>46083.90854394721</v>
       </c>
       <c r="G5" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="H5" t="n">
-        <v>1379.36</v>
+        <v>1365.38</v>
       </c>
       <c r="I5" t="n">
         <v>2.77128</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.083852068839253</v>
+        <v>0.07286708165507161</v>
       </c>
       <c r="L5" t="n">
         <v>9</v>
@@ -677,20 +677,20 @@
         <v>39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46083.86850438212</v>
+        <v>46083.90854394721</v>
       </c>
       <c r="G6" t="n">
-        <v>57.78</v>
+        <v>57.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2253.42</v>
+        <v>2258.88</v>
       </c>
       <c r="I6" t="n">
         <v>53.19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.1356132075471699</v>
+        <v>0.1383647798742138</v>
       </c>
       <c r="L6" t="n">
         <v>11</v>
@@ -717,20 +717,20 @@
         <v>170</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46083.86850438212</v>
+        <v>46083.90854394721</v>
       </c>
       <c r="G7" t="n">
-        <v>12.68</v>
+        <v>12.46</v>
       </c>
       <c r="H7" t="n">
-        <v>2155.6</v>
+        <v>2118.2</v>
       </c>
       <c r="I7" t="n">
         <v>11.412</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.07914893617021268</v>
+        <v>0.06042553191489364</v>
       </c>
       <c r="L7" t="n">
         <v>9.667</v>
@@ -757,20 +757,20 @@
         <v>89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46083.86850438212</v>
+        <v>46083.90854394721</v>
       </c>
       <c r="G8" t="n">
-        <v>22.48</v>
+        <v>22.54</v>
       </c>
       <c r="H8" t="n">
-        <v>2000.72</v>
+        <v>2006.06</v>
       </c>
       <c r="I8" t="n">
         <v>20.52</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.1545968156137649</v>
+        <v>0.157678479712378</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -797,20 +797,20 @@
         <v>312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46083.86850438212</v>
+        <v>46083.90854394721</v>
       </c>
       <c r="G9" t="n">
-        <v>6.44</v>
+        <v>6.42</v>
       </c>
       <c r="H9" t="n">
-        <v>2009.28</v>
+        <v>2003.04</v>
       </c>
       <c r="I9" t="n">
         <v>5.796</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0.144787130032886</v>
+        <v>0.1412318904986223</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>
